--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:27</t>
+    <t xml:space="preserve">2026-09-09 23:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
@@ -57,6 +57,9 @@
     <t xml:space="preserve">Punitaqui</t>
   </si>
   <si>
+    <t xml:space="preserve">Paihuano</t>
+  </si>
+  <si>
     <t xml:space="preserve">La Higuera</t>
   </si>
   <si>
@@ -75,9 +78,6 @@
     <t xml:space="preserve">Illapel</t>
   </si>
   <si>
-    <t xml:space="preserve">Paihuano</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:24</t>
+    <t xml:space="preserve">2026-09-17 14:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -636,13 +636,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4104</v>
+        <v>4105</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>16.13</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="10">
@@ -650,16 +650,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4102</v>
+        <v>4104</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13.69</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="11">
@@ -667,16 +667,16 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4203</v>
+        <v>4102</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13.61</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="12">
@@ -687,13 +687,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4204</v>
+        <v>4203</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13.17</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="13">
@@ -704,13 +704,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4103</v>
+        <v>4204</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13.01</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="14">
@@ -721,13 +721,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4101</v>
+        <v>4103</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>12.34</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="15">
@@ -738,13 +738,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4201</v>
+        <v>4101</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12.03</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="16">
@@ -755,10 +755,14 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4105</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+        <v>4201</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>12.03</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E16"/>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:19</t>
+    <t xml:space="preserve">2026-09-23 12:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:47</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre la mediana nacional (%)</t>
+    <t xml:space="preserve">% bajo 50% de la mediana</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -118,9 +118,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre mediana</t>
   </si>
 </sst>
 </file>
@@ -841,7 +838,7 @@
         <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-02 11:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:19</t>
+    <t xml:space="preserve">2026-10-02 15:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:05</t>
+    <t xml:space="preserve">2026-10-04 09:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:21</t>
+    <t xml:space="preserve">2026-10-05 12:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
